--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.77404</v>
+        <v>16.84119</v>
       </c>
       <c r="D2" t="n">
-        <v>16.64264</v>
+        <v>16.44398</v>
       </c>
       <c r="E2" t="n">
-        <v>16.96806</v>
+        <v>16.64209</v>
       </c>
       <c r="F2" t="n">
-        <v>42.34849</v>
+        <v>41.99754</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05023</v>
+        <v>0.05056</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85105</v>
+        <v>1.80186</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.31063</v>
+        <v>16.98563</v>
       </c>
       <c r="D3" t="n">
-        <v>17.11281</v>
+        <v>16.55844</v>
       </c>
       <c r="E3" t="n">
-        <v>17.01231</v>
+        <v>16.82877</v>
       </c>
       <c r="F3" t="n">
-        <v>42.34188</v>
+        <v>42.08135</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05034</v>
+        <v>0.05154</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81277</v>
+        <v>1.81814</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.55125</v>
+        <v>16.89255</v>
       </c>
       <c r="D4" t="n">
-        <v>16.54591</v>
+        <v>16.48099</v>
       </c>
       <c r="E4" t="n">
-        <v>16.79587</v>
+        <v>16.62702</v>
       </c>
       <c r="F4" t="n">
-        <v>42.57137</v>
+        <v>42.1643</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05208</v>
+        <v>0.05032</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81566</v>
+        <v>1.85355</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.70307</v>
+        <v>16.47876</v>
       </c>
       <c r="D6" t="n">
-        <v>16.35944</v>
+        <v>15.96849</v>
       </c>
       <c r="E6" t="n">
-        <v>16.25535</v>
+        <v>16.12062</v>
       </c>
       <c r="F6" t="n">
-        <v>21.46029</v>
+        <v>21.85216</v>
       </c>
       <c r="G6" t="n">
-        <v>34.19885</v>
+        <v>34.35802</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.87726</v>
+        <v>16.62369</v>
       </c>
       <c r="D7" t="n">
-        <v>15.88518</v>
+        <v>16.2708</v>
       </c>
       <c r="E7" t="n">
-        <v>16.51054</v>
+        <v>16.45537</v>
       </c>
       <c r="F7" t="n">
-        <v>21.94994</v>
+        <v>22.28843</v>
       </c>
       <c r="G7" t="n">
-        <v>34.03741</v>
+        <v>33.93606</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.41403</v>
+        <v>16.36044</v>
       </c>
       <c r="D8" t="n">
-        <v>15.69957</v>
+        <v>15.70458</v>
       </c>
       <c r="E8" t="n">
-        <v>16.87519</v>
+        <v>16.09963</v>
       </c>
       <c r="F8" t="n">
-        <v>21.77142</v>
+        <v>21.55395</v>
       </c>
       <c r="G8" t="n">
-        <v>33.77948</v>
+        <v>34.41436</v>
       </c>
     </row>
   </sheetData>
